--- a/artfynd/A 33290-2025 artfynd.xlsx
+++ b/artfynd/A 33290-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>98536608</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468760.333076167</v>
+        <v>468761</v>
       </c>
       <c r="R2" t="n">
-        <v>6593536.488891047</v>
+        <v>6593536</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -809,12 +804,7 @@
         <v>98536985</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468760.333076167</v>
+        <v>468761</v>
       </c>
       <c r="R3" t="n">
-        <v>6593536.488891047</v>
+        <v>6593536</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
